--- a/public/templates/examples/A-018-TabletopExerciseRecords-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-018-TabletopExerciseRecords-EXAMPLE-S.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -205,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -264,6 +269,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -732,7 +744,7 @@
       <c r="F6" s="21" t="n"/>
       <c r="G6" s="20" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Coverage / Scope</t>
@@ -759,7 +771,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="n"/>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Exercise #</t>
@@ -796,16 +808,14 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="82.2" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
           <t>EX-2026-01</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
+      <c r="B12" s="26">
+        <v>46093</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
@@ -833,16 +843,14 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
           <t>EX-2025-09</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
+      <c r="B13" s="26">
+        <v>45920</v>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
@@ -1009,10 +1017,8 @@
           <t>/s/ Marcus Reed</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
+      <c r="D29" s="25">
+        <v>46099</v>
       </c>
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
@@ -1033,10 +1039,8 @@
           <t>/s/ Tracy Holloway</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
+      <c r="D30" s="25">
+        <v>46099</v>
       </c>
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="13" t="n"/>
@@ -1125,10 +1129,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
+      <c r="B46" s="24">
+        <v>46099</v>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
@@ -1143,11 +1145,11 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C5:G5"/>
@@ -1161,7 +1163,6 @@
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A36:G36"/>
@@ -1179,7 +1180,7 @@
     <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>